--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26024"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="2419" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FE4D93C-2D8C-4C1C-AD53-06A48BD0F240}"/>
+  <xr:revisionPtr revIDLastSave="2431" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C78E01C-7F68-4FD1-9680-8B21AA5BD7C4}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,13 +56,6 @@
     <sheet name="0121" sheetId="42" r:id="rId46"/>
     <sheet name="0114" sheetId="41" r:id="rId47"/>
     <sheet name="0107" sheetId="40" r:id="rId48"/>
-    <sheet name="Nov21" sheetId="34" r:id="rId49"/>
-    <sheet name="Oct21" sheetId="30" r:id="rId50"/>
-    <sheet name="SEP" sheetId="26" r:id="rId51"/>
-    <sheet name="AUG" sheetId="21" r:id="rId52"/>
-    <sheet name="JUL" sheetId="16" r:id="rId53"/>
-    <sheet name="JUN" sheetId="11" r:id="rId54"/>
-    <sheet name="May" sheetId="7" r:id="rId55"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -82,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="46">
   <si>
     <t>As end of</t>
   </si>
@@ -221,18 +214,6 @@
   <si>
     <t>12-30</t>
   </si>
-  <si>
-    <t>11-30</t>
-  </si>
-  <si>
-    <t>10-29</t>
-  </si>
-  <si>
-    <t>10-21</t>
-  </si>
-  <si>
-    <t>08-20</t>
-  </si>
 </sst>
 </file>
 
@@ -293,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -304,7 +285,6 @@
     <xf numFmtId="187" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
@@ -637,7 +617,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44925</v>
       </c>
       <c r="D1" t="s">
@@ -648,7 +628,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -678,11 +658,11 @@
         <v>243000</v>
       </c>
       <c r="C4" s="7">
-        <v>-38400</v>
+        <v>-37800</v>
       </c>
       <c r="D4" s="5">
         <f>C4/B4</f>
-        <v>-0.15802469135802469</v>
+        <v>-0.15555555555555556</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -693,19 +673,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2818500</v>
+        <v>2767500</v>
       </c>
       <c r="C5" s="7">
-        <v>-564925</v>
+        <v>-538500</v>
       </c>
       <c r="D5" s="5">
         <f>C5/B5</f>
-        <v>-0.20043462834841227</v>
+        <v>-0.194579945799458</v>
       </c>
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -715,11 +695,11 @@
         <v>2734950</v>
       </c>
       <c r="C6" s="7">
-        <v>-953400</v>
+        <v>-951750</v>
       </c>
       <c r="D6" s="5">
         <f>C6/B6</f>
-        <v>-0.34859869467449128</v>
+        <v>-0.34799539296879284</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -729,15 +709,15 @@
       <c r="A7" s="4"/>
       <c r="B7" s="6">
         <f>SUM(B4:B6)</f>
-        <v>5796450</v>
+        <v>5745450</v>
       </c>
       <c r="C7" s="6">
         <f>SUM(C4:C6)</f>
-        <v>-1556725</v>
+        <v>-1528050</v>
       </c>
       <c r="D7" s="5">
         <f>C7/B7</f>
-        <v>-0.26856524251912811</v>
+        <v>-0.26595828003028482</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75">
@@ -755,11 +735,11 @@
         <v>5358300</v>
       </c>
       <c r="C9" s="7">
-        <v>-700900</v>
+        <v>-703700</v>
       </c>
       <c r="D9" s="5">
         <f>C9/B9</f>
-        <v>-0.13080641248157066</v>
+        <v>-0.13132896627661758</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -782,15 +762,15 @@
       </c>
       <c r="B11" s="6">
         <f>B7+B9</f>
-        <v>11154750</v>
+        <v>11103750</v>
       </c>
       <c r="C11" s="6">
         <f>C7+C9</f>
-        <v>-2257625</v>
+        <v>-2231750</v>
       </c>
       <c r="D11" s="5">
         <f>C11/B11</f>
-        <v>-0.20239135794168403</v>
+        <v>-0.20099065630980525</v>
       </c>
       <c r="E11">
         <f>E4+E5+E6+E9</f>
@@ -801,7 +781,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44918</v>
       </c>
       <c r="D13" t="s">
@@ -812,7 +792,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -969,7 +949,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44855</v>
       </c>
       <c r="D1" t="s">
@@ -980,7 +960,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>2.0470533963787365E-2</v>
       </c>
@@ -1037,7 +1017,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -1133,7 +1113,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44846</v>
       </c>
       <c r="D13" t="s">
@@ -1144,7 +1124,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1301,7 +1281,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44846</v>
       </c>
       <c r="D1" t="s">
@@ -1312,7 +1292,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.1639099267965317E-2</v>
       </c>
@@ -1369,7 +1349,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -1465,7 +1445,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44841</v>
       </c>
       <c r="D13" t="s">
@@ -1476,7 +1456,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-6.51144063264774E-3</v>
       </c>
     </row>
@@ -1632,7 +1612,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44841</v>
       </c>
       <c r="D1" t="s">
@@ -1643,7 +1623,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-6.51144063264774E-3</v>
       </c>
@@ -1700,7 +1680,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -1793,7 +1773,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
@@ -1804,7 +1784,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-2.5862438791206799E-2</v>
       </c>
     </row>
@@ -1960,7 +1940,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D1" t="s">
@@ -1971,7 +1951,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-2.5862438791206799E-2</v>
       </c>
@@ -2028,7 +2008,7 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -2121,7 +2101,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
@@ -2132,7 +2112,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>8.0348380765452975E-4</v>
       </c>
     </row>
@@ -2288,7 +2268,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>10</v>
       </c>
       <c r="D1" t="s">
@@ -2299,7 +2279,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>8.0348380765452975E-4</v>
       </c>
@@ -2356,7 +2336,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -2449,7 +2429,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
@@ -2460,7 +2440,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.4637802033095093E-2</v>
       </c>
     </row>
@@ -2616,7 +2596,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D1" t="s">
@@ -2627,7 +2607,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.4637802033095093E-2</v>
       </c>
@@ -2684,7 +2664,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -2777,7 +2757,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
@@ -2788,7 +2768,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>2.0016644576641988E-2</v>
       </c>
     </row>
@@ -2944,7 +2924,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D1" t="s">
@@ -2955,7 +2935,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>2.0016644576641988E-2</v>
       </c>
@@ -3012,7 +2992,7 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -3105,7 +3085,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
@@ -3116,7 +3096,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.0238387240455647E-2</v>
       </c>
     </row>
@@ -3272,7 +3252,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D1" t="s">
@@ -3283,7 +3263,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.0238387240455647E-2</v>
       </c>
@@ -3340,7 +3320,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -3434,7 +3414,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
@@ -3445,7 +3425,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-3.5567066720168712E-3</v>
       </c>
     </row>
@@ -3601,7 +3581,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" t="s">
@@ -3612,7 +3592,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-3.5567066720168712E-3</v>
       </c>
@@ -3669,7 +3649,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -3763,7 +3743,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D13" t="s">
@@ -3774,7 +3754,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>5.9282682758753903E-2</v>
       </c>
     </row>
@@ -3930,7 +3910,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D1" t="s">
@@ -3941,7 +3921,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>5.9282682758753903E-2</v>
       </c>
@@ -3998,7 +3978,7 @@
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -4092,7 +4072,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
@@ -4103,7 +4083,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-4.8324969396322196E-3</v>
       </c>
     </row>
@@ -4259,7 +4239,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44918</v>
       </c>
       <c r="D1" t="s">
@@ -4270,7 +4250,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -4327,7 +4307,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -4423,7 +4403,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44904</v>
       </c>
       <c r="D13" t="s">
@@ -4434,7 +4414,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.126928723281129E-2</v>
       </c>
     </row>
@@ -4591,7 +4571,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D1" t="s">
@@ -4602,7 +4582,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-4.8324969396322196E-3</v>
       </c>
@@ -4659,7 +4639,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -4753,7 +4733,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D13" t="s">
@@ -4764,7 +4744,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-5.1392245254506044E-3</v>
       </c>
     </row>
@@ -4920,7 +4900,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
@@ -4931,7 +4911,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-5.1392245254506044E-3</v>
       </c>
@@ -4988,7 +4968,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -5082,7 +5062,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
@@ -5093,7 +5073,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5249,7 +5229,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D1" t="s">
@@ -5260,7 +5240,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-2.7410183839469623E-4</v>
       </c>
@@ -5317,7 +5297,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -5411,7 +5391,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
@@ -5422,7 +5402,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.9561766433758707E-2</v>
       </c>
     </row>
@@ -5578,7 +5558,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D1" t="s">
@@ -5589,7 +5569,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.9561766433758707E-2</v>
       </c>
@@ -5646,7 +5626,7 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -5740,7 +5720,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
@@ -5751,7 +5731,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.994340385392801E-2</v>
       </c>
     </row>
@@ -5907,7 +5887,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D1" t="s">
@@ -5918,7 +5898,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.994340385392801E-2</v>
       </c>
@@ -5975,7 +5955,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -6069,7 +6049,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
@@ -6080,7 +6060,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -6236,7 +6216,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1" t="s">
@@ -6247,7 +6227,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-9.1341105925338093E-3</v>
       </c>
@@ -6304,7 +6284,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -6398,7 +6378,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
@@ -6409,7 +6389,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>5.4431731502670158E-3</v>
       </c>
     </row>
@@ -6565,7 +6545,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D1" t="s">
@@ -6576,7 +6556,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>5.4431731502670158E-3</v>
       </c>
@@ -6633,7 +6613,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -6727,7 +6707,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D13" t="s">
@@ -6738,7 +6718,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-3.0640915678329512E-2</v>
       </c>
     </row>
@@ -6894,7 +6874,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D1" t="s">
@@ -6905,7 +6885,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-3.0640915678329512E-2</v>
       </c>
@@ -6962,7 +6942,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -7056,7 +7036,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D13" t="s">
@@ -7067,7 +7047,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7223,7 +7203,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D1" t="s">
@@ -7234,7 +7214,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -7291,7 +7271,7 @@
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -7385,7 +7365,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
@@ -7396,7 +7376,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7552,7 +7532,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D1" t="s">
@@ -7563,7 +7543,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -7620,7 +7600,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -7714,7 +7694,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
@@ -7725,7 +7705,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7881,7 +7861,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44904</v>
       </c>
       <c r="D1" t="s">
@@ -7892,7 +7872,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.126928723281129E-2</v>
       </c>
@@ -7949,7 +7929,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -8045,7 +8025,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44897</v>
       </c>
       <c r="D13" t="s">
@@ -8056,7 +8036,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.2826682460946294E-2</v>
       </c>
     </row>
@@ -8213,7 +8193,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D1" t="s">
@@ -8224,7 +8204,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -8281,7 +8261,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -8375,7 +8355,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
@@ -8386,7 +8366,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -8542,7 +8522,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>27</v>
       </c>
       <c r="D1" t="s">
@@ -8553,7 +8533,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -8610,7 +8590,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -8704,7 +8684,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D13" t="s">
@@ -8715,7 +8695,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>9.6814267114206411E-3</v>
       </c>
     </row>
@@ -8871,7 +8851,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D1" t="s">
@@ -8882,7 +8862,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>9.6814267114206411E-3</v>
       </c>
@@ -8939,7 +8919,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -9033,7 +9013,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>29</v>
       </c>
       <c r="D13" t="s">
@@ -9044,7 +9024,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-6.9157769869514123E-3</v>
       </c>
     </row>
@@ -9200,7 +9180,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>29</v>
       </c>
       <c r="D1" t="s">
@@ -9211,7 +9191,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-6.9157769869514123E-3</v>
       </c>
@@ -9268,7 +9248,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -9362,7 +9342,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D13" t="s">
@@ -9373,7 +9353,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-5.4505556735329561E-3</v>
       </c>
     </row>
@@ -9529,7 +9509,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D1" t="s">
@@ -9540,7 +9520,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-5.4505556735329561E-3</v>
       </c>
@@ -9597,7 +9577,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -9691,7 +9671,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
@@ -9702,7 +9682,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.0997137404580186E-2</v>
       </c>
     </row>
@@ -9858,7 +9838,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D1" t="s">
@@ -9869,7 +9849,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.0997137404580186E-2</v>
       </c>
@@ -9926,7 +9906,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -10020,7 +10000,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D13" t="s">
@@ -10031,7 +10011,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.0187606865613172E-3</v>
       </c>
     </row>
@@ -10187,7 +10167,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D1" t="s">
@@ -10198,7 +10178,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.0187606865613172E-3</v>
       </c>
@@ -10255,7 +10235,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -10349,7 +10329,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
@@ -10360,7 +10340,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.2364219757420039E-2</v>
       </c>
     </row>
@@ -10516,7 +10496,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D1" t="s">
@@ -10527,7 +10507,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.2364219757420039E-2</v>
       </c>
@@ -10584,7 +10564,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -10678,7 +10658,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D13" t="s">
@@ -10689,7 +10669,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-8.2011341612231933E-3</v>
       </c>
     </row>
@@ -10845,7 +10825,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D1" t="s">
@@ -10856,7 +10836,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-8.2011341612231933E-3</v>
       </c>
@@ -10913,7 +10893,7 @@
       <c r="E5">
         <v>8</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -11007,7 +10987,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D13" t="s">
@@ -11018,7 +10998,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-7.9872773234906866E-3</v>
       </c>
     </row>
@@ -11174,7 +11154,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D1" t="s">
@@ -11185,7 +11165,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-7.9872773234906866E-3</v>
       </c>
@@ -11242,7 +11222,7 @@
       <c r="E5">
         <v>9</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -11336,7 +11316,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
@@ -11347,7 +11327,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -11503,7 +11483,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44897</v>
       </c>
       <c r="D1" t="s">
@@ -11514,7 +11494,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.2826682460946294E-2</v>
       </c>
@@ -11571,7 +11551,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -11667,7 +11647,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44890</v>
       </c>
       <c r="D13" t="s">
@@ -11678,7 +11658,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>2.1392622636608643E-3</v>
       </c>
     </row>
@@ -11835,7 +11815,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D1" t="s">
@@ -11846,7 +11826,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>3.1430442288231278E-3</v>
       </c>
@@ -11903,7 +11883,7 @@
       <c r="E5">
         <v>11</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -11997,7 +11977,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D13" t="s">
@@ -12008,7 +11988,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.9437310296521102E-2</v>
       </c>
     </row>
@@ -12164,7 +12144,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D1" t="s">
@@ -12175,7 +12155,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.9437310296521102E-2</v>
       </c>
@@ -12232,7 +12212,7 @@
       <c r="E5">
         <v>12</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -12326,7 +12306,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D13" t="s">
@@ -12337,7 +12317,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>8.2391713747645944E-3</v>
       </c>
     </row>
@@ -12493,7 +12473,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D1" t="s">
@@ -12504,7 +12484,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>8.2391713747645944E-3</v>
       </c>
@@ -12561,7 +12541,7 @@
       <c r="E5">
         <v>13</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -12655,7 +12635,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D13" t="s">
@@ -12666,7 +12646,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.4920380834060051E-2</v>
       </c>
     </row>
@@ -12822,7 +12802,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D1" t="s">
@@ -12833,7 +12813,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.4920380834060051E-2</v>
       </c>
@@ -12890,7 +12870,7 @@
       <c r="E5">
         <v>16</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -12984,7 +12964,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D13" t="s">
@@ -12995,7 +12975,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.541111468271061E-2</v>
       </c>
     </row>
@@ -13151,7 +13131,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D1" t="s">
@@ -13162,7 +13142,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.541111468271061E-2</v>
       </c>
@@ -13219,7 +13199,7 @@
       <c r="E5">
         <v>19</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -13313,7 +13293,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D13" t="s">
@@ -13324,7 +13304,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-2.3718332698021288E-3</v>
       </c>
     </row>
@@ -13480,7 +13460,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D1" t="s">
@@ -13491,7 +13471,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-2.3718332698021288E-3</v>
       </c>
@@ -13548,7 +13528,7 @@
       <c r="E5">
         <v>19</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -13642,7 +13622,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D13" t="s">
@@ -13653,7 +13633,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.1897430991910997E-2</v>
       </c>
     </row>
@@ -13809,7 +13789,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D1" t="s">
@@ -13820,7 +13800,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.1897430991910997E-2</v>
       </c>
@@ -13877,7 +13857,7 @@
       <c r="E5">
         <v>18</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -13971,7 +13951,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D13" t="s">
@@ -13982,7 +13962,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>9.0551513615908467E-3</v>
       </c>
     </row>
@@ -14138,7 +14118,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D1" t="s">
@@ -14149,7 +14129,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>9.0551513615908467E-3</v>
       </c>
@@ -14206,7 +14186,7 @@
       <c r="E5">
         <v>17</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -14300,7 +14280,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D13" t="s">
@@ -14311,7 +14291,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -14467,7 +14447,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D1" t="s">
@@ -14478,7 +14458,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>0</v>
       </c>
@@ -14535,7 +14515,7 @@
       <c r="E5">
         <v>16</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -14629,7 +14609,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>45</v>
       </c>
       <c r="D13" t="s">
@@ -14640,7 +14620,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -14772,335 +14752,6 @@
       </c>
       <c r="E23">
         <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BA8346-E5AB-45DC-B131-E47CC7D82506}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1568.69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="E2" s="10">
-        <f>(E1-E13)/E13</f>
-        <v>-3.3718731328113934E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>2104400</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-148600</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-7.0613951720205279E-2</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>4333450</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-68025</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-1.5697654293922857E-2</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>125400</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-25200</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.20095693779904306</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6563250</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-241825</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-3.684531291661905E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5213400</v>
-      </c>
-      <c r="C9" s="7">
-        <v>451657</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>8.6633866574596236E-2</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>-426450</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11776650</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9+C10</f>
-        <v>-216618</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-1.8393855638063457E-2</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1623.43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="E14" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>2769200</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-55100</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.989744330492561E-2</v>
-      </c>
-      <c r="E16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2864250</v>
-      </c>
-      <c r="C17" s="7">
-        <v>74850</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.6132495417648598E-2</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>188100</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-36000</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.19138755980861244</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5821550</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-16250</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.7913528184074689E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5263500</v>
-      </c>
-      <c r="C21" s="7">
-        <v>438065</v>
-      </c>
-      <c r="D21" s="5">
-        <v>8.3226940248883829E-2</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>-281000</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11085050</v>
-      </c>
-      <c r="C23" s="6">
-        <v>140815</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1.2703145227130234E-2</v>
-      </c>
-      <c r="E23">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -15125,7 +14776,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44890</v>
       </c>
       <c r="D1" t="s">
@@ -15136,7 +14787,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>2.1392622636608643E-3</v>
       </c>
@@ -15193,7 +14844,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -15289,7 +14940,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44883</v>
       </c>
       <c r="D13" t="s">
@@ -15300,7 +14951,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>-1.2160338119697705E-2</v>
       </c>
     </row>
@@ -15433,1466 +15084,6 @@
       </c>
       <c r="E23">
         <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956761AF-EDDA-466F-914E-EDBACCF8128C}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1643.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="E2" s="10">
-        <f>(E1-E13)/E13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>2769200</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-55100</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-1.989744330492561E-2</v>
-      </c>
-      <c r="E4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2864250</v>
-      </c>
-      <c r="C5" s="7">
-        <v>74850</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>2.6132495417648598E-2</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>188100</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-36000</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.19138755980861244</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5821550</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-16250</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-2.7913528184074689E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5263500</v>
-      </c>
-      <c r="C9" s="7">
-        <v>438065</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>8.3226940248883829E-2</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>-281000</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11085050</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9+C10</f>
-        <v>140815</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>1.2703145227130234E-2</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1643.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="E14" s="10">
-        <v>3.0394765752789349E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>2431600</v>
-      </c>
-      <c r="C16" s="7">
-        <v>900</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3.7012666556999509E-4</v>
-      </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3220250</v>
-      </c>
-      <c r="C17" s="7">
-        <v>93875</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.9151463395699091E-2</v>
-      </c>
-      <c r="E17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>188100</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-37800</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.20095693779904306</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5839950</v>
-      </c>
-      <c r="C19" s="6">
-        <v>56975</v>
-      </c>
-      <c r="D19" s="5">
-        <v>9.7560766787386875E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5181625</v>
-      </c>
-      <c r="C21" s="7">
-        <v>426815</v>
-      </c>
-      <c r="D21" s="5">
-        <v>8.2370877861674671E-2</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>-186975</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11021575</v>
-      </c>
-      <c r="C23" s="6">
-        <v>296815</v>
-      </c>
-      <c r="D23" s="5">
-        <v>2.6930361586252418E-2</v>
-      </c>
-      <c r="E23">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE05999-BE97-4C01-9411-B2F5A6F3549D}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1605.17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="E2" s="10">
-        <f>(E1-E13)/E13</f>
-        <v>-3.1762244033679864E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1588500</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-31250</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-1.9672647151400692E-2</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>4068450</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-3950</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-9.7088571814818914E-4</v>
-      </c>
-      <c r="E5">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>250800</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-60000</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.23923444976076555</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5907750</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-95200</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-1.611442596589226E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5161625</v>
-      </c>
-      <c r="C9" s="7">
-        <v>423415</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>8.2031337030489426E-2</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>-397875</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11069375</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9+C10</f>
-        <v>-69660</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-6.2930382248320253E-3</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1605.68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="E14" s="10">
-        <v>-1.5614750329522132E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1588500</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-33000</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.0774315391879131E-2</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>4012200</v>
-      </c>
-      <c r="C17" s="7">
-        <v>17300</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4.3118488609740291E-3</v>
-      </c>
-      <c r="E17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>250800</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-60000</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.23923444976076555</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5851500</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-75700</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.2936853798171409E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5064125</v>
-      </c>
-      <c r="C21" s="7">
-        <v>419015</v>
-      </c>
-      <c r="D21" s="5">
-        <v>8.2741835953891341E-2</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>-393725</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10915625</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-50410</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-4.6181505868880621E-3</v>
-      </c>
-      <c r="E23">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E3762E-C4E7-4D2A-8CA1-8DA9672A9D7D}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1638.75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="E2" s="10">
-        <f>(E1-E13)/E13</f>
-        <v>5.5093421239006381E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1870150</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-8925</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-4.7723444643477794E-3</v>
-      </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3735200</v>
-      </c>
-      <c r="C5" s="7">
-        <v>33725</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>9.0289676590276282E-3</v>
-      </c>
-      <c r="E5">
-        <v>15</v>
-      </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>250800</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-55200</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.22009569377990432</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5856150</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-30400</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-5.1911238612398934E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4999375</v>
-      </c>
-      <c r="C9" s="7">
-        <v>420482</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>8.4106913364170519E-2</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>-275375</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10855525</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9+C10</f>
-        <v>114707</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>1.0566692997344669E-2</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1553.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1675150</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-16300</v>
-      </c>
-      <c r="D16" s="5">
-        <f>C16/B16</f>
-        <v>-9.7304718980389809E-3</v>
-      </c>
-      <c r="E16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3735200</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-56125</v>
-      </c>
-      <c r="D17" s="5">
-        <f>C17/B17</f>
-        <v>-1.5025969158278004E-2</v>
-      </c>
-      <c r="E17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>864350</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-170450</v>
-      </c>
-      <c r="D18" s="5">
-        <f>C18/B18</f>
-        <v>-0.19720020824897322</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <f>SUM(B16:B18)</f>
-        <v>6274700</v>
-      </c>
-      <c r="C19" s="6">
-        <f>SUM(C16:C18)</f>
-        <v>-242875</v>
-      </c>
-      <c r="D19" s="5">
-        <f>C19/B19</f>
-        <v>-3.8707029818158635E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4999375</v>
-      </c>
-      <c r="C21" s="7">
-        <v>420482</v>
-      </c>
-      <c r="D21" s="5">
-        <f>C21/B21</f>
-        <v>8.4106913364170519E-2</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>-323500</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <f>B19+B21</f>
-        <v>11274075</v>
-      </c>
-      <c r="C23" s="6">
-        <f>C19+C21+C22</f>
-        <v>-145893</v>
-      </c>
-      <c r="D23" s="5">
-        <f>C23/B23</f>
-        <v>-1.2940573838651952E-2</v>
-      </c>
-      <c r="E23">
-        <f>E16+E17+E18+E21</f>
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90C5C96F-6BB1-44AA-8E75-C42770BBBEC9}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4">
-        <v>4</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1321000</v>
-      </c>
-      <c r="C2" s="7">
-        <v>3900</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2/B2</f>
-        <v>2.9523088569265708E-3</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7">
-        <v>3070350</v>
-      </c>
-      <c r="C3" s="7">
-        <v>-204050</v>
-      </c>
-      <c r="D3" s="5">
-        <f>C3/B3</f>
-        <v>-6.6458221375413226E-2</v>
-      </c>
-      <c r="E3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7">
-        <v>718200</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-101900</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.14188248398774714</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6">
-        <f>SUM(B2:B4)</f>
-        <v>5109550</v>
-      </c>
-      <c r="C5" s="6">
-        <f>SUM(C2:C4)</f>
-        <v>-302050</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-5.9114794844947208E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75">
-      <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7">
-        <v>6244125</v>
-      </c>
-      <c r="C7" s="7">
-        <v>487062.95</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>7.8003395191479988E-2</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7">
-        <v>-402550</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <f>B5+B7</f>
-        <v>11353675</v>
-      </c>
-      <c r="C9" s="6">
-        <f>C5+C7+C8</f>
-        <v>-217537.05</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-1.9160056105181802E-2</v>
-      </c>
-      <c r="E9">
-        <f>E2+E3+E4+E7</f>
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55ABFF5C-D713-4FD1-BDB3-C9325E6EF080}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4">
-        <v>4</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1201000</v>
-      </c>
-      <c r="C2" s="7">
-        <v>-45900</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2/B2</f>
-        <v>-3.8218151540383015E-2</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7">
-        <v>2948800</v>
-      </c>
-      <c r="C3" s="7">
-        <v>-38150</v>
-      </c>
-      <c r="D3" s="5">
-        <f>C3/B3</f>
-        <v>-1.2937466087900163E-2</v>
-      </c>
-      <c r="E3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1092600</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-195800</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.17920556470803589</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6">
-        <f>SUM(B2:B4)</f>
-        <v>5242400</v>
-      </c>
-      <c r="C5" s="6">
-        <f>SUM(C2:C4)</f>
-        <v>-279850</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-5.3382038760872885E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75">
-      <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7">
-        <v>5825800</v>
-      </c>
-      <c r="C7" s="7">
-        <v>452168</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>7.7614748189089908E-2</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <f>B5+B7</f>
-        <v>11068200</v>
-      </c>
-      <c r="C9" s="6">
-        <f>C5+C7</f>
-        <v>172318</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>1.5568746498979057E-2</v>
-      </c>
-      <c r="E9">
-        <f>E2+E3+E4+E7</f>
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E58C2AA-66F2-4116-B88D-B82E582B4972}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4">
-        <v>4</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1604000</v>
-      </c>
-      <c r="C2" s="7">
-        <v>-12000</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2/B2</f>
-        <v>-7.481296758104738E-3</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7">
-        <v>2426350</v>
-      </c>
-      <c r="C3" s="7">
-        <v>71300</v>
-      </c>
-      <c r="D3" s="5">
-        <f>C3/B3</f>
-        <v>2.9385702804624231E-2</v>
-      </c>
-      <c r="E3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7">
-        <v>558600</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-123900</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.22180451127819548</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6">
-        <f>SUM(B2:B4)</f>
-        <v>4588950</v>
-      </c>
-      <c r="C5" s="6">
-        <f>SUM(C2:C4)</f>
-        <v>-64600</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-1.4077294370171826E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75">
-      <c r="A6" s="4"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7">
-        <v>6082300</v>
-      </c>
-      <c r="C7" s="7">
-        <v>464044</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>7.6294165036252734E-2</v>
-      </c>
-      <c r="E7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.75">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <f>B5+B7</f>
-        <v>10671250</v>
-      </c>
-      <c r="C9" s="6">
-        <f>C5+C7</f>
-        <v>399444</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>3.7431791027292959E-2</v>
-      </c>
-      <c r="E9">
-        <f>E2+E3+E4+E7</f>
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -16917,7 +15108,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44883</v>
       </c>
       <c r="D1" t="s">
@@ -16928,7 +15119,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>-1.2160338119697705E-2</v>
       </c>
@@ -16985,7 +15176,7 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -17081,7 +15272,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44876</v>
       </c>
       <c r="D13" t="s">
@@ -17092,7 +15283,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>6.7452899798317841E-3</v>
       </c>
     </row>
@@ -17249,7 +15440,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44876</v>
       </c>
       <c r="D1" t="s">
@@ -17260,7 +15451,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>6.7452899798317841E-3</v>
       </c>
@@ -17317,7 +15508,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -17413,7 +15604,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44869</v>
       </c>
       <c r="D13" t="s">
@@ -17424,7 +15615,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.0915239066112997E-2</v>
       </c>
     </row>
@@ -17581,7 +15772,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44869</v>
       </c>
       <c r="D1" t="s">
@@ -17592,7 +15783,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.0915239066112997E-2</v>
       </c>
@@ -17649,7 +15840,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -17745,7 +15936,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44865</v>
       </c>
       <c r="D13" t="s">
@@ -17756,7 +15947,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.0064480483195502E-2</v>
       </c>
     </row>
@@ -17913,7 +16104,7 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>44865</v>
       </c>
       <c r="D1" t="s">
@@ -17924,7 +16115,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(E1-E13)/E13</f>
         <v>1.0064480483195502E-2</v>
       </c>
@@ -17981,7 +16172,7 @@
       <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
@@ -18077,7 +16268,7 @@
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>44855</v>
       </c>
       <c r="D13" t="s">
@@ -18088,7 +16279,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>2.0470533963787365E-2</v>
       </c>
     </row>
